--- a/users.xlsx
+++ b/users.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,6 +449,18 @@
       <c r="B2" t="inlineStr">
         <is>
           <t>$2b$12$a5y8sv57EKZPTUwbShUN8.kqttiEWG0le3N60EI.whnzjCn3XJb7m</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>morgan</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>$2b$12$AXMukV.RYj2f8Mh/M1KnAer/EdDDIunE4SeGupxLndVcrsqbRfKFO</t>
         </is>
       </c>
     </row>

--- a/users.xlsx
+++ b/users.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,6 +461,18 @@
       <c r="B3" t="inlineStr">
         <is>
           <t>$2b$12$AXMukV.RYj2f8Mh/M1KnAer/EdDDIunE4SeGupxLndVcrsqbRfKFO</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>mkroach3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>$2b$12$A/9E568VDT.5IhNpKswf3Omd2410GyyqUN.KqeE5i7q563ThLJGm.</t>
         </is>
       </c>
     </row>

--- a/users.xlsx
+++ b/users.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,6 +473,18 @@
       <c r="B4" t="inlineStr">
         <is>
           <t>$2b$12$A/9E568VDT.5IhNpKswf3Omd2410GyyqUN.KqeE5i7q563ThLJGm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Olivia1998</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>$2b$12$KbCqJAVq3nx09gggtxDPCugo8CeR8PdVqMtnN0ofZIawbd0H81gV.</t>
         </is>
       </c>
     </row>
